--- a/test_data/Data_Anna/sorptionsoil_sieving_120126-.xlsx
+++ b/test_data/Data_Anna/sorptionsoil_sieving_120126-.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/plbj_dtu_dk/Documents/Work_Projects_Oliver Lund/Programmer/Kornstørrelse - Program/test_data/Data_Anna/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="8_{7F3E39F6-76CF-417F-8662-E789E62C2A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFD6098D-DEA2-4253-8649-508766116777}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="8_{7F3E39F6-76CF-417F-8662-E789E62C2A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48B2932F-AD36-4379-8ADA-533115BCD77E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{DBB09911-16D6-4697-9313-AEBD2BE1D35E}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="17520" activeTab="5" xr2:uid="{DBB09911-16D6-4697-9313-AEBD2BE1D35E}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="1" r:id="rId1"/>
@@ -4126,6 +4126,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4712,16 +4716,16 @@
       <c r="B12" s="28"/>
       <c r="C12" s="48"/>
       <c r="D12" s="34">
-        <f t="shared" si="2"/>
+        <f>B12-C12</f>
         <v>0</v>
       </c>
       <c r="E12" s="28" t="e">
-        <f t="shared" si="0"/>
+        <f>D12/$D$22*100</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="28" t="e">
-        <f t="shared" si="1"/>
+        <f>G13+E12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K12" t="s">
